--- a/2024_DeVleeschouwer/ACE_Errors/Data/Output/Interval_stats/ACE_depth_interval_stats_all.xlsx
+++ b/2024_DeVleeschouwer/ACE_Errors/Data/Output/Interval_stats/ACE_depth_interval_stats_all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sjro/Library/CloudStorage/Dropbox/BAS/Data/R/Papers_R/2024_DeVleeschouwer/ACE_Errors/Data/Output/Interval_stats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E60050D5-897A-7C4A-9E36-0D134C98B7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E809F10-C281-7A44-AB18-90D08F490D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-43100" yWindow="1780" windowWidth="27640" windowHeight="16680" xr2:uid="{CDAA6A87-765C-1845-8B1D-2D99F9305803}"/>
+    <workbookView xWindow="-45740" yWindow="5380" windowWidth="27640" windowHeight="16680" xr2:uid="{CDAA6A87-765C-1845-8B1D-2D99F9305803}"/>
   </bookViews>
   <sheets>
     <sheet name="ACE_depth_interval_stats_all" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -210,10 +213,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -404,7 +414,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -519,6 +529,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -564,25 +594,38 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -964,54 +1007,54 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="3" max="11" width="10.83203125" style="7"/>
+    <col min="3" max="11" width="10.83203125" style="5"/>
     <col min="12" max="12" width="2.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="1:12" s="4" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" s="3" customFormat="1" ht="68" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="9" t="s">
         <v>15</v>
       </c>
       <c r="L2" s="2"/>
@@ -1021,29 +1064,31 @@
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="4">
         <v>268</v>
       </c>
-      <c r="D3" s="6">
-        <v>1</v>
-      </c>
-      <c r="E3" s="6">
+      <c r="D3" s="11">
+        <v>1.2</v>
+      </c>
+      <c r="E3" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="G3" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="H3" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="I3" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="J3" s="11">
         <v>0.3</v>
       </c>
-      <c r="F3" s="6">
-        <v>5.5</v>
-      </c>
-      <c r="G3" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="H3" s="6">
-        <v>3.3</v>
-      </c>
-      <c r="I3" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6">
+      <c r="K3" s="11">
         <v>16.5</v>
       </c>
       <c r="L3" s="1"/>
@@ -1053,31 +1098,31 @@
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>68</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="11">
         <v>1</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="11">
         <v>0.1</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="11">
         <v>7.5</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="11">
         <v>0.7</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="11">
         <v>3.7</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="11">
         <v>0.4</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="11">
         <v>1.1000000000000001</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="11">
         <v>15.9</v>
       </c>
       <c r="L4" s="1"/>
@@ -1087,31 +1132,31 @@
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>66</v>
       </c>
-      <c r="D5" s="6">
-        <v>0.6</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="D5" s="11">
+        <v>1.2</v>
+      </c>
+      <c r="E5" s="11">
         <v>0.1</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="11">
         <v>6</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="11">
         <v>0.9</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="11">
         <v>3.3</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="11">
         <v>0.4</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="11">
         <v>0.3</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="11">
         <v>16.5</v>
       </c>
       <c r="L5" s="1"/>
@@ -1121,31 +1166,31 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <v>52</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="11">
         <v>1.3</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="11">
         <v>0.1</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="11">
         <v>4.7</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="11">
         <v>0.9</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="11">
         <v>2.9</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="11">
         <v>0.4</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="11">
         <v>1.4</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="11">
         <v>10.7</v>
       </c>
       <c r="L6" s="1"/>
@@ -1155,65 +1200,65 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
         <v>51</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="11">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="11">
         <v>0.1</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="11">
         <v>4</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="11">
         <v>0.8</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="11">
         <v>1.9</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="11">
         <v>0.3</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="11">
         <v>1.2</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="11">
         <v>7.9</v>
       </c>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="7">
         <v>31</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="12">
         <v>1.2</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="12">
         <v>0.1</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="12">
         <v>3.3</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="12">
         <v>0.8</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="12">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="12">
         <v>0.4</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="12">
         <v>1.2</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="12">
         <v>8.1999999999999993</v>
       </c>
       <c r="L8" s="1"/>
@@ -1221,15 +1266,15 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
       <c r="L9" s="1"/>
     </row>
   </sheetData>
